--- a/role-expectations/ATC対応表_福田会計.xlsx
+++ b/role-expectations/ATC対応表_福田会計.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>パートナー</t>
+          <t>（執行）社員</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
